--- a/bank account management/data/categorisize_paiment.xlsx
+++ b/bank account management/data/categorisize_paiment.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25831"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Corentin\Bureau\bank account management\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Python Github\Python_proj\bank account management\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE454CBD-08B2-4E92-8DD0-57C7EA7F6EB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C79A334A-0C85-4F7A-8086-2F8E9B1F9E8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="279">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="418" uniqueCount="417">
   <si>
     <t>games</t>
   </si>
@@ -862,6 +862,420 @@
   </si>
   <si>
     <t>LUC</t>
+  </si>
+  <si>
+    <t>papa</t>
+  </si>
+  <si>
+    <t>muriel</t>
+  </si>
+  <si>
+    <t>astrid</t>
+  </si>
+  <si>
+    <t>bnp paribas</t>
+  </si>
+  <si>
+    <t>Chemins de fer</t>
+  </si>
+  <si>
+    <t>PIKORG</t>
+  </si>
+  <si>
+    <t>Schöne Bescherung</t>
+  </si>
+  <si>
+    <t>DEPOT</t>
+  </si>
+  <si>
+    <t>jakalicious</t>
+  </si>
+  <si>
+    <t>Coiffure</t>
+  </si>
+  <si>
+    <t>QIRIN</t>
+  </si>
+  <si>
+    <t>Donate</t>
+  </si>
+  <si>
+    <t>Burgermeister</t>
+  </si>
+  <si>
+    <t>Kultur Lokal Rank</t>
+  </si>
+  <si>
+    <t>Illuminarium</t>
+  </si>
+  <si>
+    <t>Kaisin</t>
+  </si>
+  <si>
+    <t>roots</t>
+  </si>
+  <si>
+    <t>Plaza Klub</t>
+  </si>
+  <si>
+    <t>Gerold's</t>
+  </si>
+  <si>
+    <t>KAUFLEUTEN</t>
+  </si>
+  <si>
+    <t>Billiardino</t>
+  </si>
+  <si>
+    <t>Osteria Borgo</t>
+  </si>
+  <si>
+    <t>SBB</t>
+  </si>
+  <si>
+    <t>Jelmoli</t>
+  </si>
+  <si>
+    <t>C &amp; A Mode</t>
+  </si>
+  <si>
+    <t>Aldi</t>
+  </si>
+  <si>
+    <t>KESSLERS CLUB</t>
+  </si>
+  <si>
+    <t>MCDONALDS</t>
+  </si>
+  <si>
+    <t>BLACK TAP</t>
+  </si>
+  <si>
+    <t>Nelson Pub</t>
+  </si>
+  <si>
+    <t>TAKE AWAY</t>
+  </si>
+  <si>
+    <t>trainline</t>
+  </si>
+  <si>
+    <t>Sofian</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ada-Lokma </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Momomo </t>
+  </si>
+  <si>
+    <t>Vagabundo</t>
+  </si>
+  <si>
+    <t>H+ HOTEL</t>
+  </si>
+  <si>
+    <t>Viola</t>
+  </si>
+  <si>
+    <t>Raclette Factory</t>
+  </si>
+  <si>
+    <t>Garibaldi</t>
+  </si>
+  <si>
+    <t>El Lokal</t>
+  </si>
+  <si>
+    <t>UJUICE</t>
+  </si>
+  <si>
+    <t>Scent of Bamboo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Schneiderei </t>
+  </si>
+  <si>
+    <t>Booking.co</t>
+  </si>
+  <si>
+    <t>travel</t>
+  </si>
+  <si>
+    <t>FLYSCOOT</t>
+  </si>
+  <si>
+    <t>DEANGELO</t>
+  </si>
+  <si>
+    <t>Prannavi</t>
+  </si>
+  <si>
+    <t>Lauriina</t>
+  </si>
+  <si>
+    <t>MRT</t>
+  </si>
+  <si>
+    <t>Jeybalasingam</t>
+  </si>
+  <si>
+    <t>Apotheke</t>
+  </si>
+  <si>
+    <t>BANK</t>
+  </si>
+  <si>
+    <t>TAO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">we for you </t>
+  </si>
+  <si>
+    <t>PEKABO</t>
+  </si>
+  <si>
+    <t>Vaudoise</t>
+  </si>
+  <si>
+    <t>Kiosk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MISTER MINIT </t>
+  </si>
+  <si>
+    <t>Micas Garten</t>
+  </si>
+  <si>
+    <t>CAMILLA</t>
+  </si>
+  <si>
+    <t>Yulia</t>
+  </si>
+  <si>
+    <t>ALESSANDRO</t>
+  </si>
+  <si>
+    <t>Remontées</t>
+  </si>
+  <si>
+    <t>JulesVerne</t>
+  </si>
+  <si>
+    <t>C+A MODE</t>
+  </si>
+  <si>
+    <t>retrait liquide</t>
+  </si>
+  <si>
+    <t>Morosani</t>
+  </si>
+  <si>
+    <t>Coiffeur</t>
+  </si>
+  <si>
+    <t>FRUUGO</t>
+  </si>
+  <si>
+    <t>Kosmos</t>
+  </si>
+  <si>
+    <t>intersportrent</t>
+  </si>
+  <si>
+    <t>Ochsner Sport</t>
+  </si>
+  <si>
+    <t>DANIEL H. FINE FOOD</t>
+  </si>
+  <si>
+    <t>JETZT GMBH</t>
+  </si>
+  <si>
+    <t>Patrick</t>
+  </si>
+  <si>
+    <t>Grab</t>
+  </si>
+  <si>
+    <t>grabtaxi</t>
+  </si>
+  <si>
+    <t>Alfamart</t>
+  </si>
+  <si>
+    <t>Cash</t>
+  </si>
+  <si>
+    <t>Getyourguide</t>
+  </si>
+  <si>
+    <t>Corentin</t>
+  </si>
+  <si>
+    <t>Battle4</t>
+  </si>
+  <si>
+    <t>Hotel</t>
+  </si>
+  <si>
+    <t>Navigo</t>
+  </si>
+  <si>
+    <t>Keolis Lyon</t>
+  </si>
+  <si>
+    <t>Tcl</t>
+  </si>
+  <si>
+    <t>Paragon</t>
+  </si>
+  <si>
+    <t>Luke's Lobster</t>
+  </si>
+  <si>
+    <t>Miguel</t>
+  </si>
+  <si>
+    <t>Ram Burger</t>
+  </si>
+  <si>
+    <t>Verve Pizza</t>
+  </si>
+  <si>
+    <t>G2000</t>
+  </si>
+  <si>
+    <t>Potato Corner</t>
+  </si>
+  <si>
+    <t>Simplygo</t>
+  </si>
+  <si>
+    <t>Cold Storage</t>
+  </si>
+  <si>
+    <t>Watson's</t>
+  </si>
+  <si>
+    <t>Pita Tree</t>
+  </si>
+  <si>
+    <t>Beach Club</t>
+  </si>
+  <si>
+    <t>Don Don Donki</t>
+  </si>
+  <si>
+    <t>flightnetw</t>
+  </si>
+  <si>
+    <t>anywheel</t>
+  </si>
+  <si>
+    <t>Natureland</t>
+  </si>
+  <si>
+    <t>Tonkotsu</t>
+  </si>
+  <si>
+    <t>The Exchange</t>
+  </si>
+  <si>
+    <t>Finest 111 Somerset</t>
+  </si>
+  <si>
+    <t>French Fold</t>
+  </si>
+  <si>
+    <t>Merci Marcel</t>
+  </si>
+  <si>
+    <t>Vietnam</t>
+  </si>
+  <si>
+    <t>reservation</t>
+  </si>
+  <si>
+    <t>Waa Cow</t>
+  </si>
+  <si>
+    <t>Ce La Vi</t>
+  </si>
+  <si>
+    <t>Ma Maison</t>
+  </si>
+  <si>
+    <t>Wise</t>
+  </si>
+  <si>
+    <t>Saladstop</t>
+  </si>
+  <si>
+    <t>Food Folks</t>
+  </si>
+  <si>
+    <t>Levant</t>
+  </si>
+  <si>
+    <t>Smoke &amp; Mirrors</t>
+  </si>
+  <si>
+    <t>Tiong Bahru Bakery</t>
+  </si>
+  <si>
+    <t>Le Noir</t>
+  </si>
+  <si>
+    <t>Kinokuniya-Takashimaya</t>
+  </si>
+  <si>
+    <t>Scoot</t>
+  </si>
+  <si>
+    <t>Marquee</t>
+  </si>
+  <si>
+    <t>celavi</t>
+  </si>
+  <si>
+    <t>H&amp;M</t>
+  </si>
+  <si>
+    <t>Banana Leaf</t>
+  </si>
+  <si>
+    <t>Employees Only</t>
+  </si>
+  <si>
+    <t>Avenue</t>
+  </si>
+  <si>
+    <t>The Flying Squirrel</t>
+  </si>
+  <si>
+    <t>Tuff Club</t>
+  </si>
+  <si>
+    <t>4fingers</t>
+  </si>
+  <si>
+    <t>J BAER GRUPPE</t>
+  </si>
+  <si>
+    <t>CREDIT COUPONS</t>
+  </si>
+  <si>
+    <t>South Korea Visa</t>
+  </si>
+  <si>
+    <t>7-Eleven</t>
+  </si>
+  <si>
+    <t>Mandai</t>
+  </si>
+  <si>
+    <t>Shabusai</t>
   </si>
 </sst>
 </file>
@@ -1179,18 +1593,38 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Y32"/>
+  <dimension ref="A1:Z68"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="17.5703125" customWidth="1"/>
+    <col min="2" max="2" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="23.42578125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="27.85546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="27.7109375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="26.42578125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="31.42578125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="10.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1266,8 +1700,11 @@
       <c r="Y1" t="s">
         <v>263</v>
       </c>
-    </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z1" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>13</v>
       </c>
@@ -1343,8 +1780,11 @@
       <c r="Y2" t="s">
         <v>264</v>
       </c>
-    </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z2" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="3" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>28</v>
       </c>
@@ -1396,6 +1836,9 @@
       <c r="Q3" t="s">
         <v>106</v>
       </c>
+      <c r="R3" t="s">
+        <v>128</v>
+      </c>
       <c r="S3" t="s">
         <v>210</v>
       </c>
@@ -1417,8 +1860,11 @@
       <c r="Y3" t="s">
         <v>265</v>
       </c>
-    </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z3" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="4" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>64</v>
       </c>
@@ -1468,7 +1914,7 @@
         <v>259</v>
       </c>
       <c r="R4" t="s">
-        <v>128</v>
+        <v>412</v>
       </c>
       <c r="T4" t="s">
         <v>43</v>
@@ -1485,8 +1931,14 @@
       <c r="X4" t="s">
         <v>204</v>
       </c>
-    </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y4" t="s">
+        <v>411</v>
+      </c>
+      <c r="Z4" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="5" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>72</v>
       </c>
@@ -1544,8 +1996,11 @@
       <c r="X5" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z5" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="6" spans="1:26" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
         <v>50</v>
       </c>
@@ -1579,6 +2034,9 @@
       <c r="N6" t="s">
         <v>95</v>
       </c>
+      <c r="P6" t="s">
+        <v>326</v>
+      </c>
       <c r="T6" t="s">
         <v>150</v>
       </c>
@@ -1591,8 +2049,11 @@
       <c r="X6" t="s">
         <v>139</v>
       </c>
-    </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z6" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="7" spans="1:26" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
         <v>124</v>
       </c>
@@ -1638,8 +2099,11 @@
       <c r="X7" t="s">
         <v>215</v>
       </c>
-    </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z7" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="8" spans="1:26" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>59</v>
       </c>
@@ -1667,20 +2131,29 @@
       <c r="K8" t="s">
         <v>26</v>
       </c>
+      <c r="L8" t="s">
+        <v>331</v>
+      </c>
       <c r="N8" t="s">
         <v>95</v>
       </c>
       <c r="T8" t="s">
         <v>38</v>
       </c>
+      <c r="U8" t="s">
+        <v>302</v>
+      </c>
       <c r="V8" t="s">
         <v>118</v>
       </c>
       <c r="X8" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z8" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>74</v>
       </c>
@@ -1693,6 +2166,9 @@
       <c r="F9" t="s">
         <v>140</v>
       </c>
+      <c r="G9" t="s">
+        <v>334</v>
+      </c>
       <c r="H9" t="s">
         <v>235</v>
       </c>
@@ -1711,14 +2187,20 @@
       <c r="T9" t="s">
         <v>24</v>
       </c>
+      <c r="U9" t="s">
+        <v>303</v>
+      </c>
       <c r="V9" t="s">
         <v>229</v>
       </c>
       <c r="X9" t="s">
         <v>207</v>
       </c>
-    </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z9" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
         <v>84</v>
       </c>
@@ -1731,6 +2213,9 @@
       <c r="F10" t="s">
         <v>159</v>
       </c>
+      <c r="G10" t="s">
+        <v>398</v>
+      </c>
       <c r="H10" t="s">
         <v>253</v>
       </c>
@@ -1749,6 +2234,9 @@
       <c r="T10" t="s">
         <v>12</v>
       </c>
+      <c r="U10" t="s">
+        <v>345</v>
+      </c>
       <c r="V10" t="s">
         <v>247</v>
       </c>
@@ -1756,7 +2244,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:26" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
         <v>85</v>
       </c>
@@ -1787,6 +2275,9 @@
       <c r="T11" t="s">
         <v>197</v>
       </c>
+      <c r="U11" t="s">
+        <v>372</v>
+      </c>
       <c r="V11" t="s">
         <v>271</v>
       </c>
@@ -1794,7 +2285,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:26" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
         <v>83</v>
       </c>
@@ -1825,20 +2316,29 @@
       <c r="T12" t="s">
         <v>200</v>
       </c>
+      <c r="U12" t="s">
+        <v>404</v>
+      </c>
       <c r="X12" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:26" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>119</v>
       </c>
+      <c r="D13" t="s">
+        <v>304</v>
+      </c>
       <c r="E13" t="s">
         <v>161</v>
       </c>
       <c r="F13" t="s">
         <v>164</v>
       </c>
+      <c r="H13" t="s">
+        <v>282</v>
+      </c>
       <c r="I13" t="s">
         <v>192</v>
       </c>
@@ -1858,16 +2358,25 @@
         <v>243</v>
       </c>
     </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:26" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
         <v>127</v>
       </c>
+      <c r="D14" t="s">
+        <v>375</v>
+      </c>
       <c r="E14" t="s">
         <v>219</v>
       </c>
       <c r="F14" t="s">
         <v>172</v>
       </c>
+      <c r="H14" t="s">
+        <v>329</v>
+      </c>
+      <c r="J14" t="s">
+        <v>288</v>
+      </c>
       <c r="K14" t="s">
         <v>63</v>
       </c>
@@ -1881,16 +2390,25 @@
         <v>273</v>
       </c>
     </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:26" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
         <v>147</v>
       </c>
+      <c r="D15" t="s">
+        <v>337</v>
+      </c>
       <c r="E15" t="s">
         <v>185</v>
       </c>
       <c r="F15" t="s">
         <v>174</v>
       </c>
+      <c r="H15" t="s">
+        <v>346</v>
+      </c>
+      <c r="J15" t="s">
+        <v>338</v>
+      </c>
       <c r="K15" t="s">
         <v>79</v>
       </c>
@@ -1900,16 +2418,28 @@
       <c r="T15" t="s">
         <v>233</v>
       </c>
-    </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="X15" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
         <v>196</v>
       </c>
+      <c r="D16" t="s">
+        <v>379</v>
+      </c>
       <c r="E16" t="s">
         <v>186</v>
       </c>
       <c r="F16" t="s">
         <v>177</v>
+      </c>
+      <c r="H16" t="s">
+        <v>358</v>
+      </c>
+      <c r="J16" t="s">
+        <v>348</v>
       </c>
       <c r="K16" t="s">
         <v>81</v>
@@ -1925,11 +2455,17 @@
       <c r="B17" t="s">
         <v>199</v>
       </c>
+      <c r="D17" t="s">
+        <v>414</v>
+      </c>
       <c r="E17" t="s">
         <v>189</v>
       </c>
       <c r="F17" t="s">
         <v>179</v>
+      </c>
+      <c r="H17" t="s">
+        <v>359</v>
       </c>
       <c r="K17" t="s">
         <v>131</v>
@@ -1951,6 +2487,9 @@
       <c r="F18" t="s">
         <v>180</v>
       </c>
+      <c r="H18" t="s">
+        <v>361</v>
+      </c>
       <c r="K18" t="s">
         <v>160</v>
       </c>
@@ -1971,6 +2510,9 @@
       <c r="F19" t="s">
         <v>181</v>
       </c>
+      <c r="H19" t="s">
+        <v>393</v>
+      </c>
       <c r="K19" t="s">
         <v>178</v>
       </c>
@@ -1997,8 +2539,14 @@
       <c r="N20" t="s">
         <v>267</v>
       </c>
+      <c r="T20" t="s">
+        <v>286</v>
+      </c>
     </row>
     <row r="21" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B21" t="s">
+        <v>283</v>
+      </c>
       <c r="E21" t="s">
         <v>212</v>
       </c>
@@ -2011,8 +2559,14 @@
       <c r="N21" t="s">
         <v>270</v>
       </c>
+      <c r="T21" t="s">
+        <v>335</v>
+      </c>
     </row>
     <row r="22" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B22" t="s">
+        <v>301</v>
+      </c>
       <c r="E22" t="s">
         <v>220</v>
       </c>
@@ -2025,8 +2579,14 @@
       <c r="N22" t="s">
         <v>278</v>
       </c>
+      <c r="T22" t="s">
+        <v>349</v>
+      </c>
     </row>
     <row r="23" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B23" t="s">
+        <v>310</v>
+      </c>
       <c r="E23" t="s">
         <v>221</v>
       </c>
@@ -2036,62 +2596,422 @@
       <c r="K23" t="s">
         <v>266</v>
       </c>
+      <c r="N23" t="s">
+        <v>279</v>
+      </c>
+      <c r="T23" t="s">
+        <v>351</v>
+      </c>
     </row>
     <row r="24" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B24" t="s">
+        <v>325</v>
+      </c>
       <c r="E24" t="s">
         <v>237</v>
       </c>
       <c r="F24" t="s">
         <v>202</v>
       </c>
+      <c r="K24" t="s">
+        <v>306</v>
+      </c>
+      <c r="N24" t="s">
+        <v>280</v>
+      </c>
+      <c r="T24" t="s">
+        <v>352</v>
+      </c>
     </row>
     <row r="25" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B25" t="s">
+        <v>343</v>
+      </c>
       <c r="E25" t="s">
         <v>245</v>
       </c>
       <c r="F25" t="s">
         <v>211</v>
       </c>
+      <c r="K25" t="s">
+        <v>309</v>
+      </c>
+      <c r="N25" t="s">
+        <v>281</v>
+      </c>
+      <c r="T25" t="s">
+        <v>382</v>
+      </c>
     </row>
     <row r="26" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B26" t="s">
+        <v>356</v>
+      </c>
       <c r="E26" t="s">
         <v>272</v>
       </c>
       <c r="F26" t="s">
         <v>224</v>
       </c>
+      <c r="K26" t="s">
+        <v>312</v>
+      </c>
+      <c r="N26" t="s">
+        <v>290</v>
+      </c>
     </row>
     <row r="27" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B27" t="s">
+        <v>357</v>
+      </c>
       <c r="E27" t="s">
         <v>276</v>
       </c>
       <c r="F27" t="s">
         <v>240</v>
       </c>
+      <c r="K27" t="s">
+        <v>313</v>
+      </c>
+      <c r="N27" t="s">
+        <v>311</v>
+      </c>
     </row>
     <row r="28" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B28" t="s">
+        <v>364</v>
+      </c>
+      <c r="E28" t="s">
+        <v>287</v>
+      </c>
       <c r="F28" t="s">
         <v>241</v>
       </c>
+      <c r="K28" t="s">
+        <v>367</v>
+      </c>
+      <c r="N28" t="s">
+        <v>316</v>
+      </c>
     </row>
     <row r="29" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B29" t="s">
+        <v>365</v>
+      </c>
+      <c r="E29" t="s">
+        <v>289</v>
+      </c>
       <c r="F29" t="s">
         <v>249</v>
       </c>
+      <c r="K29" t="s">
+        <v>368</v>
+      </c>
+      <c r="N29" t="s">
+        <v>328</v>
+      </c>
     </row>
     <row r="30" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B30" t="s">
+        <v>366</v>
+      </c>
+      <c r="E30" t="s">
+        <v>291</v>
+      </c>
       <c r="F30" t="s">
         <v>268</v>
       </c>
+      <c r="K30" t="s">
+        <v>377</v>
+      </c>
+      <c r="N30" t="s">
+        <v>327</v>
+      </c>
     </row>
     <row r="31" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B31" t="s">
+        <v>374</v>
+      </c>
+      <c r="E31" t="s">
+        <v>294</v>
+      </c>
       <c r="F31" t="s">
         <v>269</v>
       </c>
+      <c r="K31" t="s">
+        <v>385</v>
+      </c>
+      <c r="N31" t="s">
+        <v>330</v>
+      </c>
     </row>
     <row r="32" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B32" t="s">
+        <v>380</v>
+      </c>
+      <c r="E32" t="s">
+        <v>295</v>
+      </c>
       <c r="F32" t="s">
         <v>275</v>
+      </c>
+      <c r="K32" t="s">
+        <v>410</v>
+      </c>
+      <c r="N32" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="33" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B33" t="s">
+        <v>381</v>
+      </c>
+      <c r="E33" t="s">
+        <v>298</v>
+      </c>
+      <c r="F33" t="s">
+        <v>284</v>
+      </c>
+      <c r="N33" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="34" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B34" t="s">
+        <v>401</v>
+      </c>
+      <c r="E34" t="s">
+        <v>300</v>
+      </c>
+      <c r="F34" t="s">
+        <v>285</v>
+      </c>
+      <c r="N34" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="35" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="E35" t="s">
+        <v>307</v>
+      </c>
+      <c r="F35" t="s">
+        <v>292</v>
+      </c>
+      <c r="N35" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="36" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="E36" t="s">
+        <v>315</v>
+      </c>
+      <c r="F36" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="37" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="E37" t="s">
+        <v>317</v>
+      </c>
+      <c r="F37" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="38" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="E38" t="s">
+        <v>321</v>
+      </c>
+      <c r="F38" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="39" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="E39" t="s">
+        <v>362</v>
+      </c>
+      <c r="F39" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="40" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="E40" t="s">
+        <v>370</v>
+      </c>
+      <c r="F40" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="41" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="E41" t="s">
+        <v>371</v>
+      </c>
+      <c r="F41" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="42" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="E42" t="s">
+        <v>373</v>
+      </c>
+      <c r="F42" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="43" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="E43" t="s">
+        <v>376</v>
+      </c>
+      <c r="F43" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="44" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="E44" t="s">
+        <v>383</v>
+      </c>
+      <c r="F44" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="45" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="E45" t="s">
+        <v>386</v>
+      </c>
+      <c r="F45" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="46" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="E46" t="s">
+        <v>387</v>
+      </c>
+      <c r="F46" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="47" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="E47" t="s">
+        <v>392</v>
+      </c>
+      <c r="F47" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="48" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="E48" t="s">
+        <v>394</v>
+      </c>
+      <c r="F48" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="49" spans="5:6" x14ac:dyDescent="0.25">
+      <c r="E49" t="s">
+        <v>395</v>
+      </c>
+      <c r="F49" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="50" spans="5:6" x14ac:dyDescent="0.25">
+      <c r="E50" t="s">
+        <v>408</v>
+      </c>
+      <c r="F50" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="51" spans="5:6" x14ac:dyDescent="0.25">
+      <c r="E51" t="s">
+        <v>416</v>
+      </c>
+      <c r="F51" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="52" spans="5:6" x14ac:dyDescent="0.25">
+      <c r="F52" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="53" spans="5:6" x14ac:dyDescent="0.25">
+      <c r="F53" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="54" spans="5:6" x14ac:dyDescent="0.25">
+      <c r="F54" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="55" spans="5:6" x14ac:dyDescent="0.25">
+      <c r="F55" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="56" spans="5:6" x14ac:dyDescent="0.25">
+      <c r="F56" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="57" spans="5:6" x14ac:dyDescent="0.25">
+      <c r="F57" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="58" spans="5:6" x14ac:dyDescent="0.25">
+      <c r="F58" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="59" spans="5:6" x14ac:dyDescent="0.25">
+      <c r="F59" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="60" spans="5:6" x14ac:dyDescent="0.25">
+      <c r="F60" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="61" spans="5:6" x14ac:dyDescent="0.25">
+      <c r="F61" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="62" spans="5:6" x14ac:dyDescent="0.25">
+      <c r="F62" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="63" spans="5:6" x14ac:dyDescent="0.25">
+      <c r="F63" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="64" spans="5:6" x14ac:dyDescent="0.25">
+      <c r="F64" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="65" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F65" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="66" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F66" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="67" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F67" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="68" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F68" t="s">
+        <v>409</v>
       </c>
     </row>
   </sheetData>

--- a/bank account management/data/categorisize_paiment.xlsx
+++ b/bank account management/data/categorisize_paiment.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25831"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26227"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Python Github\Python_proj\bank account management\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C79A334A-0C85-4F7A-8086-2F8E9B1F9E8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D520C3C6-9DD0-4675-BA0D-5DAC8D3FECDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38280" yWindow="2910" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="418" uniqueCount="417">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="437" uniqueCount="436">
   <si>
     <t>games</t>
   </si>
@@ -213,9 +213,6 @@
     <t>WIX</t>
   </si>
   <si>
-    <t>MIE</t>
-  </si>
-  <si>
     <t>BOULANGERIE</t>
   </si>
   <si>
@@ -1276,6 +1273,66 @@
   </si>
   <si>
     <t>Shabusai</t>
+  </si>
+  <si>
+    <t>JUMBO</t>
+  </si>
+  <si>
+    <t>Armando</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F&amp;B Sandra AG </t>
+  </si>
+  <si>
+    <t>Suan Long</t>
+  </si>
+  <si>
+    <t>Betreibungsamt Zuri</t>
+  </si>
+  <si>
+    <t>Danka</t>
+  </si>
+  <si>
+    <t>LES HALLES</t>
+  </si>
+  <si>
+    <t>migrolino</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> IBS de Luxe GmbH</t>
+  </si>
+  <si>
+    <t>STRELAALP AG</t>
+  </si>
+  <si>
+    <t>WWW.PARTY</t>
+  </si>
+  <si>
+    <t>Guillaume</t>
+  </si>
+  <si>
+    <t>Sofien</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AMBOSS RAMPE </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rheinfelder Bierhal </t>
+  </si>
+  <si>
+    <t>DISPLATE</t>
+  </si>
+  <si>
+    <t>LIGHTINTHEBOXEU</t>
+  </si>
+  <si>
+    <t>Caffè Rist.dei Comm</t>
+  </si>
+  <si>
+    <t>les halles</t>
+  </si>
+  <si>
+    <t>Noldin Immobilien</t>
   </si>
 </sst>
 </file>
@@ -1593,7 +1650,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Z68"/>
+  <dimension ref="A1:Z73"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.140625" bestFit="1" customWidth="1"/>
@@ -1644,10 +1701,10 @@
         <v>5</v>
       </c>
       <c r="G1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="I1" t="s">
         <v>35</v>
@@ -1659,49 +1716,49 @@
         <v>53</v>
       </c>
       <c r="L1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="M1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="N1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="O1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="P1" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q1" t="s">
         <v>104</v>
       </c>
-      <c r="Q1" t="s">
-        <v>105</v>
-      </c>
       <c r="R1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="S1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="T1" t="s">
         <v>6</v>
       </c>
       <c r="U1" t="s">
+        <v>166</v>
+      </c>
+      <c r="V1" t="s">
         <v>167</v>
       </c>
-      <c r="V1" t="s">
+      <c r="W1" t="s">
         <v>168</v>
       </c>
-      <c r="W1" t="s">
-        <v>169</v>
-      </c>
       <c r="X1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="Y1" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="Z1" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
@@ -1742,46 +1799,46 @@
         <v>21</v>
       </c>
       <c r="M2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="N2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="O2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="P2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="Q2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="R2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="S2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="T2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="U2" t="s">
         <v>44</v>
       </c>
       <c r="V2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="W2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="X2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="Y2" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="Z2" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="3" spans="1:26" x14ac:dyDescent="0.25">
@@ -1804,16 +1861,16 @@
         <v>17</v>
       </c>
       <c r="G3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="I3" t="s">
         <v>25</v>
       </c>
       <c r="J3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="K3" t="s">
         <v>52</v>
@@ -1822,25 +1879,25 @@
         <v>46</v>
       </c>
       <c r="M3" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="N3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="O3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="P3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="Q3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="R3" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="S3" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="T3" t="s">
         <v>31</v>
@@ -1849,30 +1906,30 @@
         <v>40</v>
       </c>
       <c r="V3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="W3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="X3" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="Y3" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="Z3" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="4" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B4" t="s">
         <v>32</v>
       </c>
       <c r="C4" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D4" t="s">
         <v>47</v>
@@ -1881,40 +1938,40 @@
         <v>57</v>
       </c>
       <c r="F4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G4" t="s">
         <v>41</v>
       </c>
       <c r="H4" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="I4" t="s">
         <v>29</v>
       </c>
       <c r="J4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="K4" t="s">
         <v>39</v>
       </c>
       <c r="L4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="N4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="O4" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="P4" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="Q4" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="R4" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="T4" t="s">
         <v>43</v>
@@ -1923,24 +1980,24 @@
         <v>37</v>
       </c>
       <c r="V4" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="W4" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="X4" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="Y4" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="Z4" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="5" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B5" t="s">
         <v>49</v>
@@ -1952,52 +2009,52 @@
         <v>58</v>
       </c>
       <c r="F5" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G5" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="H5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="I5" t="s">
         <v>36</v>
       </c>
       <c r="J5" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="K5" t="s">
         <v>18</v>
       </c>
       <c r="L5" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="N5" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="O5" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="P5" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="T5" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="U5" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="V5" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="W5" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="X5" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="Z5" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="6" spans="1:26" x14ac:dyDescent="0.25">
@@ -2005,102 +2062,111 @@
         <v>50</v>
       </c>
       <c r="D6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E6" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F6" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G6" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="H6" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="I6" t="s">
         <v>61</v>
       </c>
       <c r="J6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K6" t="s">
         <v>19</v>
       </c>
       <c r="L6" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="N6" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="P6" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="T6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="U6" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="V6" t="s">
         <v>48</v>
       </c>
+      <c r="W6" t="s">
+        <v>416</v>
+      </c>
       <c r="X6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="Z6" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="7" spans="1:26" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E7" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G7" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="H7" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I7" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="J7" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="K7" t="s">
         <v>20</v>
       </c>
       <c r="L7" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="N7" t="s">
-        <v>96</v>
+        <v>95</v>
+      </c>
+      <c r="P7" t="s">
+        <v>435</v>
       </c>
       <c r="T7" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="U7" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="V7" t="s">
         <v>11</v>
       </c>
+      <c r="W7" t="s">
+        <v>431</v>
+      </c>
       <c r="X7" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="Z7" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="8" spans="1:26" x14ac:dyDescent="0.25">
@@ -2108,910 +2174,968 @@
         <v>59</v>
       </c>
       <c r="D8" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E8" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G8" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="H8" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="J8" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="K8" t="s">
         <v>26</v>
       </c>
       <c r="L8" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="N8" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="T8" t="s">
         <v>38</v>
       </c>
       <c r="U8" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="V8" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="X8" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="Z8" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="9" spans="1:26" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D9" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E9" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F9" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="G9" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="H9" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="I9" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="J9" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="K9" t="s">
         <v>30</v>
       </c>
       <c r="N9" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="T9" t="s">
         <v>24</v>
       </c>
       <c r="U9" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="V9" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="X9" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="Z9" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="10" spans="1:26" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D10" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F10" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="G10" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H10" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="I10" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="J10" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="K10" t="s">
         <v>55</v>
       </c>
       <c r="N10" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="T10" t="s">
         <v>12</v>
       </c>
       <c r="U10" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="V10" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="X10" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="11" spans="1:26" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D11" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E11" t="s">
+        <v>144</v>
+      </c>
+      <c r="F11" t="s">
+        <v>161</v>
+      </c>
+      <c r="G11" t="s">
+        <v>423</v>
+      </c>
+      <c r="H11" t="s">
+        <v>261</v>
+      </c>
+      <c r="I11" t="s">
         <v>145</v>
       </c>
-      <c r="F11" t="s">
-        <v>162</v>
-      </c>
-      <c r="H11" t="s">
-        <v>262</v>
-      </c>
-      <c r="I11" t="s">
-        <v>146</v>
-      </c>
       <c r="J11" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="K11" t="s">
         <v>56</v>
       </c>
       <c r="N11" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="T11" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="U11" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="V11" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="X11" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="12" spans="1:26" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D12" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E12" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F12" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H12" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="I12" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="J12" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="K12" t="s">
         <v>60</v>
       </c>
       <c r="N12" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="T12" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="U12" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="X12" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="13" spans="1:26" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D13" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E13" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="F13" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="H13" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="I13" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="J13" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="K13" t="s">
         <v>62</v>
       </c>
       <c r="N13" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="T13" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="X13" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="14" spans="1:26" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D14" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="E14" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F14" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H14" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="J14" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="K14" t="s">
-        <v>63</v>
+        <v>78</v>
       </c>
       <c r="N14" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="T14" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="X14" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="15" spans="1:26" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D15" t="s">
+        <v>336</v>
+      </c>
+      <c r="E15" t="s">
+        <v>184</v>
+      </c>
+      <c r="F15" t="s">
+        <v>173</v>
+      </c>
+      <c r="H15" t="s">
+        <v>345</v>
+      </c>
+      <c r="J15" t="s">
         <v>337</v>
       </c>
-      <c r="E15" t="s">
-        <v>185</v>
-      </c>
-      <c r="F15" t="s">
-        <v>174</v>
-      </c>
-      <c r="H15" t="s">
-        <v>346</v>
-      </c>
-      <c r="J15" t="s">
-        <v>338</v>
-      </c>
       <c r="K15" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="N15" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="T15" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="X15" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="16" spans="1:26" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D16" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="E16" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F16" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H16" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="J16" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="K16" t="s">
-        <v>81</v>
+        <v>130</v>
       </c>
       <c r="N16" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="T16" t="s">
-        <v>242</v>
+        <v>241</v>
+      </c>
+      <c r="X16" t="s">
+        <v>420</v>
       </c>
     </row>
     <row r="17" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D17" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="E17" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F17" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H17" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="K17" t="s">
-        <v>131</v>
+        <v>159</v>
       </c>
       <c r="N17" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="T17" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="18" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E18" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F18" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H18" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="K18" t="s">
-        <v>160</v>
+        <v>177</v>
       </c>
       <c r="N18" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="T18" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="19" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E19" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F19" t="s">
+        <v>180</v>
+      </c>
+      <c r="H19" t="s">
+        <v>392</v>
+      </c>
+      <c r="K19" t="s">
         <v>181</v>
       </c>
-      <c r="H19" t="s">
-        <v>393</v>
-      </c>
-      <c r="K19" t="s">
-        <v>178</v>
-      </c>
       <c r="N19" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="T19" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="20" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B20" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="E20" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F20" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="K20" t="s">
-        <v>182</v>
+        <v>205</v>
       </c>
       <c r="N20" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="T20" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="21" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="E21" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F21" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="K21" t="s">
-        <v>206</v>
+        <v>250</v>
       </c>
       <c r="N21" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="T21" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="22" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="E22" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F22" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="K22" t="s">
-        <v>251</v>
+        <v>265</v>
       </c>
       <c r="N22" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="T22" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="23" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="E23" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="F23" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="K23" t="s">
-        <v>266</v>
+        <v>305</v>
       </c>
       <c r="N23" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="T23" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="24" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B24" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="E24" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="F24" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="K24" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="N24" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="T24" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="25" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B25" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="E25" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="F25" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="K25" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="N25" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="T25" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="26" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B26" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="E26" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="F26" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="K26" t="s">
         <v>312</v>
       </c>
       <c r="N26" t="s">
-        <v>290</v>
+        <v>289</v>
+      </c>
+      <c r="T26" t="s">
+        <v>426</v>
       </c>
     </row>
     <row r="27" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B27" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="E27" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F27" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="K27" t="s">
-        <v>313</v>
+        <v>366</v>
       </c>
       <c r="N27" t="s">
-        <v>311</v>
+        <v>310</v>
+      </c>
+      <c r="T27" t="s">
+        <v>432</v>
       </c>
     </row>
     <row r="28" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B28" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="E28" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="F28" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="K28" t="s">
         <v>367</v>
       </c>
       <c r="N28" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="29" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B29" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="E29" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="F29" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="K29" t="s">
-        <v>368</v>
+        <v>376</v>
       </c>
       <c r="N29" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="30" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B30" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="E30" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="F30" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="K30" t="s">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="N30" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="31" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B31" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="E31" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="F31" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="K31" t="s">
-        <v>385</v>
+        <v>409</v>
       </c>
       <c r="N31" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="32" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B32" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="E32" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="F32" t="s">
-        <v>275</v>
-      </c>
-      <c r="K32" t="s">
-        <v>410</v>
+        <v>274</v>
       </c>
       <c r="N32" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="33" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B33" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="E33" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="F33" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="N33" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="34" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B34" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="E34" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="F34" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="N34" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="35" spans="2:14" x14ac:dyDescent="0.25">
       <c r="E35" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="F35" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="N35" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="36" spans="2:14" x14ac:dyDescent="0.25">
       <c r="E36" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F36" t="s">
-        <v>293</v>
+        <v>292</v>
+      </c>
+      <c r="N36" t="s">
+        <v>421</v>
       </c>
     </row>
     <row r="37" spans="2:14" x14ac:dyDescent="0.25">
       <c r="E37" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="F37" t="s">
-        <v>296</v>
+        <v>295</v>
+      </c>
+      <c r="N37" t="s">
+        <v>427</v>
       </c>
     </row>
     <row r="38" spans="2:14" x14ac:dyDescent="0.25">
       <c r="E38" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F38" t="s">
-        <v>297</v>
+        <v>296</v>
+      </c>
+      <c r="N38" t="s">
+        <v>428</v>
       </c>
     </row>
     <row r="39" spans="2:14" x14ac:dyDescent="0.25">
       <c r="E39" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="F39" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="40" spans="2:14" x14ac:dyDescent="0.25">
       <c r="E40" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="F40" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="41" spans="2:14" x14ac:dyDescent="0.25">
       <c r="E41" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="F41" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="42" spans="2:14" x14ac:dyDescent="0.25">
       <c r="E42" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="F42" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="43" spans="2:14" x14ac:dyDescent="0.25">
       <c r="E43" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="F43" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="44" spans="2:14" x14ac:dyDescent="0.25">
       <c r="E44" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="F44" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="45" spans="2:14" x14ac:dyDescent="0.25">
       <c r="E45" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="F45" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.25">
       <c r="E46" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="F46" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="47" spans="2:14" x14ac:dyDescent="0.25">
       <c r="E47" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="F47" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="48" spans="2:14" x14ac:dyDescent="0.25">
       <c r="E48" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="F48" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="49" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E49" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="F49" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="50" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E50" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="F50" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="51" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E51" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="F51" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="52" spans="5:6" x14ac:dyDescent="0.25">
+      <c r="E52" t="s">
+        <v>418</v>
+      </c>
       <c r="F52" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="53" spans="5:6" x14ac:dyDescent="0.25">
+      <c r="E53" t="s">
+        <v>419</v>
+      </c>
       <c r="F53" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="54" spans="5:6" x14ac:dyDescent="0.25">
+      <c r="E54" t="s">
+        <v>425</v>
+      </c>
+      <c r="F54" t="s">
         <v>353</v>
       </c>
     </row>
-    <row r="54" spans="5:6" x14ac:dyDescent="0.25">
-      <c r="F54" t="s">
-        <v>354</v>
-      </c>
-    </row>
     <row r="55" spans="5:6" x14ac:dyDescent="0.25">
+      <c r="E55" t="s">
+        <v>430</v>
+      </c>
       <c r="F55" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="56" spans="5:6" x14ac:dyDescent="0.25">
+      <c r="E56" t="s">
+        <v>433</v>
+      </c>
       <c r="F56" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="57" spans="5:6" x14ac:dyDescent="0.25">
       <c r="F57" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="58" spans="5:6" x14ac:dyDescent="0.25">
       <c r="F58" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="59" spans="5:6" x14ac:dyDescent="0.25">
       <c r="F59" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="60" spans="5:6" x14ac:dyDescent="0.25">
       <c r="F60" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="61" spans="5:6" x14ac:dyDescent="0.25">
       <c r="F61" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="62" spans="5:6" x14ac:dyDescent="0.25">
       <c r="F62" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="63" spans="5:6" x14ac:dyDescent="0.25">
       <c r="F63" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="64" spans="5:6" x14ac:dyDescent="0.25">
       <c r="F64" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="65" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F65" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="66" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F66" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="67" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F67" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="68" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F68" t="s">
-        <v>409</v>
+        <v>408</v>
+      </c>
+    </row>
+    <row r="69" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F69" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="70" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F70" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="71" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F71" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="72" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F72" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="73" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F73" t="s">
+        <v>434</v>
       </c>
     </row>
   </sheetData>
